--- a/Elin_Elinikki/LangMod/EN/Dialog/Drama/drama_elinikki_echo_stage_3.xlsx
+++ b/Elin_Elinikki/LangMod/EN/Dialog/Drama/drama_elinikki_echo_stage_3.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M23"/>
+  <dimension ref="A1:M29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -595,193 +595,265 @@
       </c>
     </row>
     <row r="13">
-      <c r="G13" t="inlineStr">
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>eval</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Elin_QuestMod.Drama.DramaRuntime.ResolveRun("cmd.elinikki.audio.se.play.elinikki_echo_clap");</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>eval</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Elin_QuestMod.Drama.DramaRuntime.ResolveRun("cmd.elinikki.audio.se.play.elinikki_echo_clap");</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>eval</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Elin_QuestMod.Drama.DramaRuntime.ResolveRun("cmd.elinikki.audio.se.play.elinikki_echo_clap");</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>eval</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Elin_QuestMod.Drama.DramaRuntime.ResolveRun("cmd.elinikki.audio.se.play.elinikki_echo_return");</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>eval</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Elin_QuestMod.Drama.DramaRuntime.ResolveRun("cmd.elinikki.audio.se.play.elinikki_echo_return");</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>eval</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Elin_QuestMod.Drama.DramaRuntime.ResolveRun("cmd.elinikki.audio.se.play.elinikki_echo_return");</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="G19" t="inlineStr">
         <is>
           <t>narrator</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t>echo3_sora_count</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="J19" t="inlineStr">
         <is>
           <t>ソラ:「三秒後……三回、返ってきた」</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="K19" t="inlineStr">
         <is>
           <t>Sora: 'Three seconds later... three claps came back.'</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
         <is>
           <t>Sora: 'Three seconds later... three claps came back.'</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="G14" t="inlineStr">
+    <row r="20">
+      <c r="G20" t="inlineStr">
         <is>
           <t>narrator</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="I20" t="inlineStr">
         <is>
           <t>echo3_sora_count_preserved</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="J20" t="inlineStr">
         <is>
           <t>ソラ:「回数まで合ってる」</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
+      <c r="K20" t="inlineStr">
         <is>
           <t>Sora: 'The count matches.'</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
         <is>
           <t>Sora: 'The count matches.'</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="G15" t="inlineStr">
+    <row r="21">
+      <c r="G21" t="inlineStr">
         <is>
           <t>narrator</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="I21" t="inlineStr">
         <is>
           <t>echo3_mina_reflection</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
+      <c r="J21" t="inlineStr">
         <is>
           <t>ミナ:「反射で回数が保存されるのは……」</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
+      <c r="K21" t="inlineStr">
         <is>
           <t>Mina: 'Reflection preserving the count...'</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
         <is>
           <t>Mina: 'Reflection preserving the count...'</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="G16" t="inlineStr">
+    <row r="22">
+      <c r="G22" t="inlineStr">
         <is>
           <t>narrator</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
+      <c r="I22" t="inlineStr">
         <is>
           <t>echo3_sora_one_more</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
+      <c r="J22" t="inlineStr">
         <is>
           <t>ソラ:「ありえなくはない。だがもう一つ試す」</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
+      <c r="K22" t="inlineStr">
         <is>
           <t>Sora: 'Possible. I'm running one more test.'</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
         <is>
           <t>Sora: 'Possible. I'm running one more test.'</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="G17" t="inlineStr">
+    <row r="23">
+      <c r="G23" t="inlineStr">
         <is>
           <t>narrator</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
+      <c r="I23" t="inlineStr">
         <is>
           <t>echo3_mina_resign</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
+      <c r="J23" t="inlineStr">
         <is>
           <t>ミナ:「……好きにしろ」</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr">
+      <c r="K23" t="inlineStr">
         <is>
           <t>Mina: '...Do what you want.'</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
         <is>
           <t>Mina: '...Do what you want.'</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="B18" t="inlineStr">
+    <row r="24">
+      <c r="B24" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
+    <row r="25">
+      <c r="A25" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="E20" t="inlineStr">
+    <row r="26">
+      <c r="E26" t="inlineStr">
         <is>
           <t>setFlag</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t>chitsii.elinikki.quest.state.echo_experiment,3</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="E21" t="inlineStr">
+    <row r="27">
+      <c r="E27" t="inlineStr">
         <is>
           <t>fadeOut</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="F27" t="inlineStr">
         <is>
           <t>0.3,black</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="E22" t="inlineStr">
+    <row r="28">
+      <c r="E28" t="inlineStr">
         <is>
           <t>setBG</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="E23" t="inlineStr">
+      <c r="F28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="E29" t="inlineStr">
         <is>
           <t>end</t>
         </is>
